--- a/economics/Economic_Assessment_Group3.xlsx
+++ b/economics/Economic_Assessment_Group3.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="106">
   <si>
     <t xml:space="preserve">Economic Assessment — Group 3 geothermal binary plant</t>
   </si>
@@ -73,6 +73,15 @@
     <t xml:space="preserve">from ORC_Group3.xlsx &gt; Base_Case_Group3!B17</t>
   </si>
   <si>
+    <t xml:space="preserve">Average Production Temperature (°C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">°C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validated FEFLOW post-processing output (Stage 12), t = 100 yr; see ../outputs/Average_Production_Temperature.csv, ../figures/F8_average_production_temperature.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">UNIT COSTS (from Xodo lecture, Zero-Emission Binary CAPEX table)</t>
   </si>
   <si>
@@ -98,6 +107,9 @@
   </si>
   <si>
     <t xml:space="preserve">€/m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scaled from Xodo reference example (2,500 m, &gt;250 degC); linear depth-scaling assumption applied to Group 3 (1,120 m wells)</t>
   </si>
   <si>
     <t xml:space="preserve">Long production testing</t>
@@ -337,11 +349,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="12">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0&quot; €&quot;"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="#,##0&quot; €/kW&quot;"/>
-    <numFmt numFmtId="168" formatCode="#,##0&quot; kW&quot;"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0&quot; €&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0&quot; €/kW&quot;"/>
+    <numFmt numFmtId="169" formatCode="#,##0&quot; kW&quot;"/>
     <numFmt numFmtId="170" formatCode="#,##0&quot; €/kW-yr&quot;"/>
     <numFmt numFmtId="171" formatCode="#,##0&quot; h/yr&quot;"/>
     <numFmt numFmtId="172" formatCode="#,##0.0&quot; €/MWh&quot;"/>
@@ -349,7 +361,7 @@
     <numFmt numFmtId="174" formatCode="0%"/>
     <numFmt numFmtId="175" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -408,13 +420,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -487,96 +492,100 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -656,7 +665,6 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -671,14 +679,14 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr sz="1800" b="1" u="none" strike="noStrike">
+              <a:rPr lang="en-US" sz="1800" b="1" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>LCOE Sensitivity — Spider Diagram (Group 3)</a:t>
+              <a:t> LCOE Spider Diagram </a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -701,7 +709,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sensitivity!C4</c:f>
+              <c:f>Sensitivity!$C$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -732,36 +740,31 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="12600">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
+                <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
@@ -795,19 +798,19 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>291.670975006444</c:v>
+                  <c:v>294.205381211103</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>226.314914675121</c:v>
+                  <c:v>228.030966631161</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>185.274075135268</c:v>
+                  <c:v>186.521696718949</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>157.569955272</c:v>
+                  <c:v>158.525671343925</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>137.86753657404</c:v>
+                  <c:v>138.625693697318</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -819,7 +822,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sensitivity!E4</c:f>
+              <c:f>Sensitivity!$E$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -850,36 +853,31 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="12600">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
+                <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
@@ -913,19 +911,19 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>177.790007925684</c:v>
+                  <c:v>178.907854076065</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>181.085139999594</c:v>
+                  <c:v>182.259925240325</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>185.274075135268</c:v>
+                  <c:v>186.521696718949</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>190.487444881876</c:v>
+                  <c:v>191.832547542768</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>196.906585470638</c:v>
+                  <c:v>198.374651581898</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -937,7 +935,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sensitivity!G4</c:f>
+              <c:f>Sensitivity!$G$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -968,36 +966,31 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="12600">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
+                <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
@@ -1031,19 +1024,19 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>220.04003480769</c:v>
+                  <c:v>221.601571266304</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>200.725612767455</c:v>
+                  <c:v>202.113645175113</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>185.274075135268</c:v>
+                  <c:v>186.521696718949</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>172.631907981659</c:v>
+                  <c:v>173.767570860652</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>162.096768686986</c:v>
+                  <c:v>163.137792992729</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1055,7 +1048,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sensitivity!I4</c:f>
+              <c:f>Sensitivity!$I$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1086,36 +1079,31 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="12600">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
+                <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
@@ -1149,19 +1137,19 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>168.953365512434</c:v>
+                  <c:v>170.055983549665</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>177.113720323851</c:v>
+                  <c:v>178.289643925912</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>185.274075135268</c:v>
+                  <c:v>186.521696718949</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>193.434429946684</c:v>
+                  <c:v>194.756964678406</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>201.594784758101</c:v>
+                  <c:v>202.990625054653</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1173,7 +1161,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sensitivity!K4</c:f>
+              <c:f>Sensitivity!$K$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1204,36 +1192,31 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="12600">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
+                <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
@@ -1267,19 +1250,19 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>168.953365512434</c:v>
+                  <c:v>170.055983549665</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>177.113720323851</c:v>
+                  <c:v>178.289643925912</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>185.274075135268</c:v>
+                  <c:v>186.521696718949</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>193.434429946684</c:v>
+                  <c:v>194.756964678406</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>201.594784758101</c:v>
+                  <c:v>202.990625054653</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1294,51 +1277,18 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="89615472"/>
-        <c:axId val="94215449"/>
+        <c:axId val="47898974"/>
+        <c:axId val="46132162"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="89615472"/>
+        <c:axId val="47898974"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr sz="1000" b="1" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Variation from base case</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -1364,7 +1314,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94215449"/>
+        <c:crossAx val="46132162"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1372,57 +1322,14 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94215449"/>
+        <c:axId val="46132162"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr sz="1000" b="1" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>LCOE [€/MWh]</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -1448,7 +1355,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89615472"/>
+        <c:crossAx val="47898974"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1730,9 +1637,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>448200</xdr:colOff>
+      <xdr:colOff>447480</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>149760</xdr:rowOff>
+      <xdr:rowOff>149040</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1740,8 +1647,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="2300760"/>
-        <a:ext cx="7919640" cy="3959640"/>
+        <a:off x="0" y="2200320"/>
+        <a:ext cx="7918920" cy="3768480"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1935,388 +1842,398 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="55"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <f aca="false">B5+B6</f>
         <v>10</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="5" t="n">
         <v>1120</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>4261.8</v>
-      </c>
-      <c r="C10" s="0" t="s">
+      <c r="B10" s="5" t="n">
+        <v>4223.9</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="B11" s="6" t="n">
+        <v>124.5327</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="D11" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="5" t="n">
         <v>20000</v>
       </c>
-      <c r="C13" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="4" t="n">
+      <c r="C13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="5" t="n">
         <v>700000</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>750000</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D26" s="3"/>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="3"/>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>400000</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="2" t="e">
-        <f aca="false">5,500,0 € / 2,500 m (Xodo example well)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C17" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>750000</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>400000</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="2"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D26" s="2"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C28" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="C29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="3"/>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="C29" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="2"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" s="0" t="n">
+      <c r="D30" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="1" t="n">
         <f aca="false">B30*8760</f>
         <v>8322</v>
       </c>
-      <c r="C31" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="D31" s="2"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="B32" s="4" t="n">
+      <c r="C31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="3"/>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C32" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="D32" s="2"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="4" t="n">
+      <c r="C32" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="3"/>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C33" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="B34" s="0" t="n">
+      <c r="C33" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="1" t="n">
         <f aca="false">B28*(1+B28)^B29/((1+B28)^B29-1)</f>
         <v>0.117459624772546</v>
       </c>
-      <c r="C34" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>56</v>
+      <c r="C34" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2341,332 +2258,332 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="0" t="n">
+    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="1" t="n">
         <f aca="false">Assumptions!B10/(1-Assumptions!B25)/1000</f>
-        <v>5.01388235294118</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="6" t="s">
+        <v>4.96929411764706</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="B6" s="8" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="C6" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="0" t="n">
+      <c r="D6" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="1" t="n">
         <f aca="false">Assumptions!B24</f>
         <v>10</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="9" t="n">
         <f aca="false">Assumptions!B13</f>
         <v>20000</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="9" t="n">
         <f aca="false">C7*D7</f>
         <v>200000</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="10" t="n">
         <f aca="false">E7/$E$18</f>
-        <v>0.00384484033735081</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="B8" s="0" t="s">
+        <v>0.0038514430450868</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <f aca="false">Assumptions!B8</f>
         <v>2</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="9" t="n">
         <f aca="false">Assumptions!B14</f>
         <v>700000</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="9" t="n">
         <f aca="false">C8*D8</f>
         <v>1400000</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="10" t="n">
         <f aca="false">E8/$E$18</f>
-        <v>0.0269138823614557</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="0" t="s">
+        <v>0.0269601013156076</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <f aca="false">Assumptions!B7</f>
         <v>10</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="9" t="n">
         <f aca="false">Assumptions!B15</f>
         <v>400000</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E9" s="9" t="n">
         <f aca="false">C9*D9</f>
         <v>4000000</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="10" t="n">
         <f aca="false">E9/$E$18</f>
-        <v>0.0768968067470163</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="0" t="n">
+        <v>0.0770288609017361</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="1" t="n">
         <f aca="false">Assumptions!B7*Assumptions!B9</f>
         <v>11200</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="9" t="n">
         <f aca="false">Assumptions!B16</f>
         <v>2200</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E10" s="9" t="n">
         <f aca="false">C10*D10</f>
         <v>24640000</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" s="10" t="n">
         <f aca="false">E10/$E$18</f>
-        <v>0.47368432956162</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="0" t="n">
+        <v>0.474497783154694</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="9" t="n">
         <f aca="false">Assumptions!B17</f>
         <v>500000</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="9" t="n">
         <f aca="false">C11*D11</f>
         <v>500000</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="10" t="n">
         <f aca="false">E11/$E$18</f>
-        <v>0.00961210084337704</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="0" t="n">
+        <v>0.00962860761271701</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="1" t="n">
         <f aca="false">B4</f>
-        <v>5.01388235294118</v>
-      </c>
-      <c r="D12" s="7" t="n">
+        <v>4.96929411764706</v>
+      </c>
+      <c r="D12" s="9" t="n">
         <f aca="false">Assumptions!B18</f>
         <v>2000000</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="9" t="n">
         <f aca="false">C12*D12</f>
-        <v>10027764.7058824</v>
-      </c>
-      <c r="F12" s="8" t="n">
+        <v>9938588.23529412</v>
+      </c>
+      <c r="F12" s="10" t="n">
         <f aca="false">E12/$E$18</f>
-        <v>0.192775771173197</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="0" t="n">
+        <v>0.191389532684025</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="9" t="n">
         <f aca="false">Assumptions!B19</f>
         <v>500000</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="9" t="n">
         <f aca="false">C13*D13</f>
         <v>500000</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="10" t="n">
         <f aca="false">E13/$E$18</f>
-        <v>0.00961210084337704</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+        <v>0.00962860761271701</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B14" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="9" t="n">
         <f aca="false">Assumptions!B20</f>
         <v>750000</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" s="9" t="n">
         <f aca="false">C14*D14</f>
         <v>750000</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="10" t="n">
         <f aca="false">E14/$E$18</f>
-        <v>0.0144181512650656</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" s="0" t="n">
+        <v>0.0144429114190755</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="1" t="n">
         <f aca="false">Assumptions!B5</f>
         <v>5</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="9" t="n">
         <f aca="false">Assumptions!B21</f>
         <v>400000</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E15" s="9" t="n">
         <f aca="false">C15*D15</f>
         <v>2000000</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="10" t="n">
         <f aca="false">E15/$E$18</f>
-        <v>0.0384484033735081</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" s="0" t="n">
+        <v>0.0385144304508681</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="1" t="n">
         <f aca="false">Assumptions!B8</f>
         <v>2</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="9" t="n">
         <f aca="false">Assumptions!B22</f>
         <v>3000000</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="E16" s="9" t="n">
         <f aca="false">C16*D16</f>
         <v>6000000</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="10" t="n">
         <f aca="false">E16/$E$18</f>
-        <v>0.115345210120524</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="0" t="n">
+        <v>0.115543291352604</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="9" t="n">
         <f aca="false">Assumptions!B23</f>
         <v>2000000</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="E17" s="9" t="n">
         <f aca="false">C17*D17</f>
         <v>2000000</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="10" t="n">
         <f aca="false">E17/$E$18</f>
-        <v>0.0384484033735081</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="12" t="n">
+        <v>0.0385144304508681</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="14" t="n">
         <f aca="false">SUM(E7:E17)</f>
-        <v>52017764.7058824</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20" s="13" t="n">
+        <v>51928588.2352941</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="15" t="n">
         <f aca="false">E18/Assumptions!B10</f>
-        <v>12205.5855990151</v>
+        <v>12293.9909172315</v>
       </c>
     </row>
   </sheetData>
@@ -2686,92 +2603,92 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="B4" s="7" t="n">
+    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="9" t="n">
         <f aca="false">CAPEX_Group3!E18</f>
-        <v>52017764.7058824</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="14" t="n">
+        <v>51928588.2352941</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="16" t="n">
         <f aca="false">Assumptions!B10</f>
-        <v>4261.8</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="13" t="n">
+        <v>4223.9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="15" t="n">
         <f aca="false">B4/B5</f>
-        <v>12205.5855990151</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="15" t="n">
+        <v>12293.9909172315</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <f aca="false">Assumptions!B34</f>
         <v>0.117459624772546</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="16" t="n">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="17" t="n">
         <f aca="false">Assumptions!B33</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="17" t="n">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="18" t="n">
         <f aca="false">Assumptions!B31</f>
         <v>8322</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="18" t="n">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="19" t="n">
         <f aca="false">Assumptions!B32</f>
         <v>13</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="B12" s="20" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="21" t="n">
         <f aca="false">(B6*B7+B8)/B9*1000+B10</f>
-        <v>185.273913072518</v>
+        <v>186.521696718949</v>
       </c>
     </row>
   </sheetData>
@@ -2791,264 +2708,269 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="6" t="s">
+    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="6" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E4" s="6" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="E4" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="F4" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="G4" s="8" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="n">
+      <c r="H4" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="22" t="n">
         <v>-0.2</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="C5" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((100)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((100)-(50))/LN((273.15+(100))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((100)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((100)-(50))/LN((273.15+(100))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>291.670975006444</v>
-      </c>
-      <c r="D5" s="0" t="n">
+      <c r="B5" s="1" t="n">
+        <f aca="false">Assumptions!$B$11*(1+A5)</f>
+        <v>99.62616</v>
+      </c>
+      <c r="C5" s="23" t="n">
+        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((B5)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B5)-(50))/LN((273.15+(B5))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((B5)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B5)-(50))/LN((273.15+(B5))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>294.205381211103</v>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="E5" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((125)-(40)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(40))/LN((273.15+(125))/(273.15+(40)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((125)-(40)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(40))/LN((273.15+(125))/(273.15+(40)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>177.790007925684</v>
-      </c>
-      <c r="F5" s="0" t="n">
+      <c r="E5" s="23" t="n">
+        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(40)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(40))/LN((273.15+(Assumptions!$B$11))/(273.15+(40)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(40)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(40))/LN((273.15+(Assumptions!$B$11))/(273.15+(40)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>178.907854076065</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="G5" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((120)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((120)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>220.04003480769</v>
-      </c>
-      <c r="H5" s="0" t="n">
+      <c r="G5" s="23" t="n">
+        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((120)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((120)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>221.601571266304</v>
+      </c>
+      <c r="H5" s="1" t="n">
         <v>896</v>
       </c>
-      <c r="I5" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(896)*10)+(2000000*(((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>168.953365512434</v>
-      </c>
-      <c r="J5" s="0" t="n">
+      <c r="I5" s="23" t="n">
+        <f aca="false">(((17350000+((2200)*(896)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>170.055983549665</v>
+      </c>
+      <c r="J5" s="1" t="n">
         <v>1760</v>
       </c>
-      <c r="K5" s="22" t="n">
-        <f aca="false">(((17350000+((1760)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>168.953365512434</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="n">
+      <c r="K5" s="23" t="n">
+        <f aca="false">(((17350000+((1760)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>170.055983549665</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="n">
         <v>-0.1</v>
       </c>
-      <c r="B6" s="0" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="C6" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((112.5)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((112.5)-(50))/LN((273.15+(112.5))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((112.5)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((112.5)-(50))/LN((273.15+(112.5))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>226.314914675121</v>
-      </c>
-      <c r="D6" s="0" t="n">
+      <c r="B6" s="1" t="n">
+        <f aca="false">Assumptions!$B$11*(1+A6)</f>
+        <v>112.07943</v>
+      </c>
+      <c r="C6" s="23" t="n">
+        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((B6)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B6)-(50))/LN((273.15+(B6))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((B6)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B6)-(50))/LN((273.15+(B6))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>228.030966631161</v>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="E6" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((125)-(45)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(45))/LN((273.15+(125))/(273.15+(45)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((125)-(45)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(45))/LN((273.15+(125))/(273.15+(45)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>181.085139999594</v>
-      </c>
-      <c r="F6" s="0" t="n">
+      <c r="E6" s="23" t="n">
+        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(45)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(45))/LN((273.15+(Assumptions!$B$11))/(273.15+(45)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(45)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(45))/LN((273.15+(Assumptions!$B$11))/(273.15+(45)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>182.259925240325</v>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>135</v>
       </c>
-      <c r="G6" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((135)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((135)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>200.725612767455</v>
-      </c>
-      <c r="H6" s="0" t="n">
+      <c r="G6" s="23" t="n">
+        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((135)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((135)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>202.113645175113</v>
+      </c>
+      <c r="H6" s="1" t="n">
         <v>1008</v>
       </c>
-      <c r="I6" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1008)*10)+(2000000*(((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>177.113720323851</v>
-      </c>
-      <c r="J6" s="0" t="n">
+      <c r="I6" s="23" t="n">
+        <f aca="false">(((17350000+((2200)*(1008)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>178.289643925912</v>
+      </c>
+      <c r="J6" s="1" t="n">
         <v>1980</v>
       </c>
-      <c r="K6" s="22" t="n">
-        <f aca="false">(((17350000+((1980)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>177.113720323851</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="n">
+      <c r="K6" s="23" t="n">
+        <f aca="false">(((17350000+((1980)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>178.289643925912</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>125</v>
-      </c>
-      <c r="C7" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>185.274075135268</v>
-      </c>
-      <c r="D7" s="0" t="n">
+      <c r="B7" s="6" t="n">
+        <f aca="false">Assumptions!$B$11</f>
+        <v>124.5327</v>
+      </c>
+      <c r="C7" s="23" t="n">
+        <f aca="false">LCOE_Group3!$B$12</f>
+        <v>186.521696718949</v>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="E7" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>185.274075135268</v>
-      </c>
-      <c r="F7" s="0" t="n">
+      <c r="E7" s="23" t="n">
+        <f aca="false">LCOE_Group3!$B$12</f>
+        <v>186.521696718949</v>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="G7" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>185.274075135268</v>
-      </c>
-      <c r="H7" s="0" t="n">
+      <c r="G7" s="23" t="n">
+        <f aca="false">LCOE_Group3!$B$12</f>
+        <v>186.521696718949</v>
+      </c>
+      <c r="H7" s="1" t="n">
         <v>1120</v>
       </c>
-      <c r="I7" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>185.274075135268</v>
-      </c>
-      <c r="J7" s="0" t="n">
+      <c r="I7" s="23" t="n">
+        <f aca="false">LCOE_Group3!$B$12</f>
+        <v>186.521696718949</v>
+      </c>
+      <c r="J7" s="1" t="n">
         <v>2200</v>
       </c>
-      <c r="K7" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>185.274075135268</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="n">
+      <c r="K7" s="23" t="n">
+        <f aca="false">LCOE_Group3!$B$12</f>
+        <v>186.521696718949</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="22" t="n">
         <v>0.1</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>137.5</v>
-      </c>
-      <c r="C8" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((137.5)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((137.5)-(50))/LN((273.15+(137.5))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((137.5)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((137.5)-(50))/LN((273.15+(137.5))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>157.569955272</v>
-      </c>
-      <c r="D8" s="0" t="n">
+      <c r="B8" s="1" t="n">
+        <f aca="false">Assumptions!$B$11*(1+A8)</f>
+        <v>136.98597</v>
+      </c>
+      <c r="C8" s="23" t="n">
+        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((B8)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B8)-(50))/LN((273.15+(B8))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((B8)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B8)-(50))/LN((273.15+(B8))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>158.525671343925</v>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="E8" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((125)-(55)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(55))/LN((273.15+(125))/(273.15+(55)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((125)-(55)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(55))/LN((273.15+(125))/(273.15+(55)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>190.487444881876</v>
-      </c>
-      <c r="F8" s="0" t="n">
+      <c r="E8" s="23" t="n">
+        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(55)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(55))/LN((273.15+(Assumptions!$B$11))/(273.15+(55)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(55)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(55))/LN((273.15+(Assumptions!$B$11))/(273.15+(55)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>191.832547542768</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>165</v>
       </c>
-      <c r="G8" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((165)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((165)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>172.631907981659</v>
-      </c>
-      <c r="H8" s="0" t="n">
+      <c r="G8" s="23" t="n">
+        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((165)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((165)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>173.767570860652</v>
+      </c>
+      <c r="H8" s="1" t="n">
         <v>1232</v>
       </c>
-      <c r="I8" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1232)*10)+(2000000*(((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>193.434429946684</v>
-      </c>
-      <c r="J8" s="0" t="n">
+      <c r="I8" s="23" t="n">
+        <f aca="false">(((17350000+((2200)*(1232)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>194.756964678406</v>
+      </c>
+      <c r="J8" s="1" t="n">
         <v>2420</v>
       </c>
-      <c r="K8" s="22" t="n">
-        <f aca="false">(((17350000+((2420)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>193.434429946684</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="n">
+      <c r="K8" s="23" t="n">
+        <f aca="false">(((17350000+((2420)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>194.756964678406</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="22" t="n">
         <v>0.2</v>
       </c>
-      <c r="B9" s="0" t="n">
-        <v>150</v>
-      </c>
-      <c r="C9" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((150)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((150)-(50))/LN((273.15+(150))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((150)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((150)-(50))/LN((273.15+(150))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>137.86753657404</v>
-      </c>
-      <c r="D9" s="0" t="n">
+      <c r="B9" s="1" t="n">
+        <f aca="false">Assumptions!$B$11*(1+A9)</f>
+        <v>149.43924</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((B9)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B9)-(50))/LN((273.15+(B9))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((B9)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B9)-(50))/LN((273.15+(B9))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>138.625693697318</v>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="E9" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((125)-(60)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(60))/LN((273.15+(125))/(273.15+(60)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((125)-(60)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(60))/LN((273.15+(125))/(273.15+(60)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>196.906585470638</v>
-      </c>
-      <c r="F9" s="0" t="n">
+      <c r="E9" s="23" t="n">
+        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(60)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(60))/LN((273.15+(Assumptions!$B$11))/(273.15+(60)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(60)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(60))/LN((273.15+(Assumptions!$B$11))/(273.15+(60)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>198.374651581898</v>
+      </c>
+      <c r="F9" s="1" t="n">
         <v>180</v>
       </c>
-      <c r="G9" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((180)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((180)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>162.096768686986</v>
-      </c>
-      <c r="H9" s="0" t="n">
+      <c r="G9" s="23" t="n">
+        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((180)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((180)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>163.137792992729</v>
+      </c>
+      <c r="H9" s="1" t="n">
         <v>1344</v>
       </c>
-      <c r="I9" s="22" t="n">
-        <f aca="false">(((17350000+((2200)*(1344)*10)+(2000000*(((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>201.594784758101</v>
-      </c>
-      <c r="J9" s="0" t="n">
+      <c r="I9" s="23" t="n">
+        <f aca="false">(((17350000+((2200)*(1344)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>202.990625054653</v>
+      </c>
+      <c r="J9" s="1" t="n">
         <v>2640</v>
       </c>
-      <c r="K9" s="22" t="n">
-        <f aca="false">(((17350000+((2640)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((125)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((125)-(50))/LN((273.15+(125))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>201.594784758101</v>
+      <c r="K9" s="23" t="n">
+        <f aca="false">(((17350000+((2640)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>202.990625054653</v>
       </c>
     </row>
   </sheetData>

--- a/economics/Economic_Assessment_Group3.xlsx
+++ b/economics/Economic_Assessment_Group3.xlsx
@@ -1,20 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIP\update\Group3_automation\economics\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBDEB70B-F3EF-400C-94AD-273ABAC41378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="3"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Assumptions" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="CAPEX_Group3" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="LCOE_Group3" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
+    <sheet name="CAPEX_Group3" sheetId="2" r:id="rId2"/>
+    <sheet name="LCOE_Group3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sensitivity" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -25,343 +41,341 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="106">
   <si>
-    <t xml:space="preserve">Economic Assessment — Group 3 geothermal binary plant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit costs derived from Dr. Luca Xodo's lecture (Zero-Emission Binary example, slide 75-79); quantities scaled to Group 3's plant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLANT / WELLFIELD DATA (Group 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production wells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5+5 doublet configuration (FEFLOW tutorial layout)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Injection wells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total wells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Well pads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 production pad + 1 injection pad (wells clustered by welldata X,Y)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Well depth (bottom of screen)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geoth_tutorial_data_Group3.xlsx &gt; welldata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net electrical power (Pel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">from ORC_Group3.xlsx &gt; Base_Case_Group3!B17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average Production Temperature (°C)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">°C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validated FEFLOW post-processing output (Stage 12), t = 100 yr; see ../outputs/Average_Production_Temperature.csv, ../figures/F8_average_production_temperature.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIT COSTS (from Xodo lecture, Zero-Emission Binary CAPEX table)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Land acquisition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">€/ha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPC of well pad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">€/pad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design &amp; management per well</t>
-  </si>
-  <si>
-    <t xml:space="preserve">€/well</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Well drilling &amp; testing (unit cost/m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">€/m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scaled from Xodo reference example (2,500 m, &gt;250 degC); linear depth-scaling assumption applied to Group 3 (1,120 m wells)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Long production testing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">€ (lump)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPC of power plant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">€/MWg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substation &amp; grid connection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gathering system design &amp; mgmt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Well pumps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">€/well (production wells)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piping &amp; equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">€/wellpad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Permitting &amp; surface exploration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Land area assumed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">same as Xodo example (2 wellpads)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORC plant auxiliaries (gross-&gt;net)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assumption, matches Xodo binary example</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FINANCIAL PARAMETERS (Xodo Business Plan defaults)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discount rate (i)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plant useful life (n)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capacity factor (CF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,322 h/yr availability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Availability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">h/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variable O&amp;M cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">€/MWh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed O&amp;M cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">€/kW-yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assumption per lecture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capital Recovery Factor (CRF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRF = i(1+i)^n / ((1+i)^n - 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPEX Breakdown — Group 3 Geothermal Binary Plant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Structure and unit costs from Xodo lecture (Zero-Emission Binary example); quantities from Assumptions sheet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gross plant capacity (MWg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit cost [€]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total cost [€]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% of total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Land acquisition and preparation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPC of well pads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design &amp; management (all wells)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Well drilling &amp; testing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m (total)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lump</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPC of the power plant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MWg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substation and grid connection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gathering: design &amp; management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gathering: well pumps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n (prod. wells)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gathering: piping &amp; equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per wellpad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Permitting and surface exploration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL CAPEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPEX per kW net installed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simplified LCOE — Group 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sLCOE = (CAPEX/kW x CRF + Fixed O&amp;M) / (8760 x CF) x 1000 + Variable O&amp;M   [Xodo lecture, based on NREL simplified LCOE]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total CAPEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net electrical power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPEX per kW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCOE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensitivity Analysis — LCOE Spider Diagram (Group 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each parameter varied ±20%/±10% independently, all others held at base case. LMTair (condenser side) held fixed at base-case value (19.959 °C).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T_source-in [°C]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCOE (Tin)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T_source-out [°C]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCOE (Tout)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flow rate [l/s]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCOE (Flow)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Well depth [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCOE (Depth)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drilling cost [€/m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCOE (DrillCost)</t>
+    <t>Economic Assessment — Group 3 geothermal binary plant</t>
+  </si>
+  <si>
+    <t>Unit costs derived from Dr. Luca Xodo's lecture (Zero-Emission Binary example, slide 75-79); quantities scaled to Group 3's plant.</t>
+  </si>
+  <si>
+    <t>PLANT / WELLFIELD DATA (Group 3)</t>
+  </si>
+  <si>
+    <t>Production wells</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>5+5 doublet configuration (FEFLOW tutorial layout)</t>
+  </si>
+  <si>
+    <t>Injection wells</t>
+  </si>
+  <si>
+    <t>Total wells</t>
+  </si>
+  <si>
+    <t>Well pads</t>
+  </si>
+  <si>
+    <t>1 production pad + 1 injection pad (wells clustered by welldata X,Y)</t>
+  </si>
+  <si>
+    <t>Well depth (bottom of screen)</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>geoth_tutorial_data_Group3.xlsx &gt; welldata</t>
+  </si>
+  <si>
+    <t>Net electrical power (Pel)</t>
+  </si>
+  <si>
+    <t>kW</t>
+  </si>
+  <si>
+    <t>from ORC_Group3.xlsx &gt; Base_Case_Group3!B17</t>
+  </si>
+  <si>
+    <t>Average Production Temperature (°C)</t>
+  </si>
+  <si>
+    <t>°C</t>
+  </si>
+  <si>
+    <t>Validated FEFLOW post-processing output (Stage 12), t = 100 yr; see ../outputs/Average_Production_Temperature.csv, ../figures/F8_average_production_temperature.png</t>
+  </si>
+  <si>
+    <t>UNIT COSTS (from Xodo lecture, Zero-Emission Binary CAPEX table)</t>
+  </si>
+  <si>
+    <t>Land acquisition</t>
+  </si>
+  <si>
+    <t>€/ha</t>
+  </si>
+  <si>
+    <t>EPC of well pad</t>
+  </si>
+  <si>
+    <t>€/pad</t>
+  </si>
+  <si>
+    <t>Design &amp; management per well</t>
+  </si>
+  <si>
+    <t>€/well</t>
+  </si>
+  <si>
+    <t>Well drilling &amp; testing (unit cost/m)</t>
+  </si>
+  <si>
+    <t>€/m</t>
+  </si>
+  <si>
+    <t>Scaled from Xodo reference example (2,500 m, &gt;250 degC); linear depth-scaling assumption applied to Group 3 (1,120 m wells)</t>
+  </si>
+  <si>
+    <t>Long production testing</t>
+  </si>
+  <si>
+    <t>€ (lump)</t>
+  </si>
+  <si>
+    <t>EPC of power plant</t>
+  </si>
+  <si>
+    <t>€/MWg</t>
+  </si>
+  <si>
+    <t>Substation &amp; grid connection</t>
+  </si>
+  <si>
+    <t>Gathering system design &amp; mgmt</t>
+  </si>
+  <si>
+    <t>Well pumps</t>
+  </si>
+  <si>
+    <t>€/well (production wells)</t>
+  </si>
+  <si>
+    <t>Piping &amp; equipment</t>
+  </si>
+  <si>
+    <t>€/wellpad</t>
+  </si>
+  <si>
+    <t>Permitting &amp; surface exploration</t>
+  </si>
+  <si>
+    <t>Land area assumed</t>
+  </si>
+  <si>
+    <t>ha</t>
+  </si>
+  <si>
+    <t>same as Xodo example (2 wellpads)</t>
+  </si>
+  <si>
+    <t>ORC plant auxiliaries (gross-&gt;net)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>assumption, matches Xodo binary example</t>
+  </si>
+  <si>
+    <t>FINANCIAL PARAMETERS (Xodo Business Plan defaults)</t>
+  </si>
+  <si>
+    <t>Discount rate (i)</t>
+  </si>
+  <si>
+    <t>Plant useful life (n)</t>
+  </si>
+  <si>
+    <t>years</t>
+  </si>
+  <si>
+    <t>Capacity factor (CF)</t>
+  </si>
+  <si>
+    <t>8,322 h/yr availability</t>
+  </si>
+  <si>
+    <t>Availability</t>
+  </si>
+  <si>
+    <t>h/yr</t>
+  </si>
+  <si>
+    <t>Variable O&amp;M cost</t>
+  </si>
+  <si>
+    <t>€/MWh</t>
+  </si>
+  <si>
+    <t>Fixed O&amp;M cost</t>
+  </si>
+  <si>
+    <t>€/kW-yr</t>
+  </si>
+  <si>
+    <t>assumption per lecture</t>
+  </si>
+  <si>
+    <t>Capital Recovery Factor (CRF)</t>
+  </si>
+  <si>
+    <t>CRF = i(1+i)^n / ((1+i)^n - 1)</t>
+  </si>
+  <si>
+    <t>CAPEX Breakdown — Group 3 Geothermal Binary Plant</t>
+  </si>
+  <si>
+    <t>Structure and unit costs from Xodo lecture (Zero-Emission Binary example); quantities from Assumptions sheet.</t>
+  </si>
+  <si>
+    <t>Gross plant capacity (MWg)</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Unit cost [€]</t>
+  </si>
+  <si>
+    <t>Total cost [€]</t>
+  </si>
+  <si>
+    <t>% of total</t>
+  </si>
+  <si>
+    <t>Land acquisition and preparation</t>
+  </si>
+  <si>
+    <t>EPC of well pads</t>
+  </si>
+  <si>
+    <t>Design &amp; management (all wells)</t>
+  </si>
+  <si>
+    <t>Well drilling &amp; testing</t>
+  </si>
+  <si>
+    <t>m (total)</t>
+  </si>
+  <si>
+    <t>lump</t>
+  </si>
+  <si>
+    <t>EPC of the power plant</t>
+  </si>
+  <si>
+    <t>MWg</t>
+  </si>
+  <si>
+    <t>Substation and grid connection</t>
+  </si>
+  <si>
+    <t>Gathering: design &amp; management</t>
+  </si>
+  <si>
+    <t>Gathering: well pumps</t>
+  </si>
+  <si>
+    <t>n (prod. wells)</t>
+  </si>
+  <si>
+    <t>Gathering: piping &amp; equipment</t>
+  </si>
+  <si>
+    <t>per wellpad</t>
+  </si>
+  <si>
+    <t>Permitting and surface exploration</t>
+  </si>
+  <si>
+    <t>TOTAL CAPEX</t>
+  </si>
+  <si>
+    <t>CAPEX per kW net installed</t>
+  </si>
+  <si>
+    <t>Simplified LCOE — Group 3</t>
+  </si>
+  <si>
+    <t>sLCOE = (CAPEX/kW x CRF + Fixed O&amp;M) / (8760 x CF) x 1000 + Variable O&amp;M   [Xodo lecture, based on NREL simplified LCOE]</t>
+  </si>
+  <si>
+    <t>Total CAPEX</t>
+  </si>
+  <si>
+    <t>Net electrical power</t>
+  </si>
+  <si>
+    <t>CAPEX per kW</t>
+  </si>
+  <si>
+    <t>LCOE</t>
+  </si>
+  <si>
+    <t>Sensitivity Analysis — LCOE Spider Diagram (Group 3)</t>
+  </si>
+  <si>
+    <t>Each parameter varied ±20%/±10% independently, all others held at base case. LMTair (condenser side) held fixed at base-case value (19.959 °C).</t>
+  </si>
+  <si>
+    <t>Variation</t>
+  </si>
+  <si>
+    <t>T_source-in [°C]</t>
+  </si>
+  <si>
+    <t>LCOE (Tin)</t>
+  </si>
+  <si>
+    <t>T_source-out [°C]</t>
+  </si>
+  <si>
+    <t>LCOE (Tout)</t>
+  </si>
+  <si>
+    <t>Flow rate [l/s]</t>
+  </si>
+  <si>
+    <t>LCOE (Flow)</t>
+  </si>
+  <si>
+    <t>Well depth [m]</t>
+  </si>
+  <si>
+    <t>LCOE (Depth)</t>
+  </si>
+  <si>
+    <t>Drilling cost [€/m]</t>
+  </si>
+  <si>
+    <t>LCOE (DrillCost)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="12">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="#,##0&quot; €&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="#,##0&quot; €/kW&quot;"/>
-    <numFmt numFmtId="169" formatCode="#,##0&quot; kW&quot;"/>
-    <numFmt numFmtId="170" formatCode="#,##0&quot; €/kW-yr&quot;"/>
-    <numFmt numFmtId="171" formatCode="#,##0&quot; h/yr&quot;"/>
-    <numFmt numFmtId="172" formatCode="#,##0.0&quot; €/MWh&quot;"/>
-    <numFmt numFmtId="173" formatCode="0.0&quot; €/MWh&quot;"/>
-    <numFmt numFmtId="174" formatCode="0%"/>
-    <numFmt numFmtId="175" formatCode="0.0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="10">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot; €&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="#,##0&quot; €/kW&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0&quot; kW&quot;"/>
+    <numFmt numFmtId="169" formatCode="#,##0&quot; €/kW-yr&quot;"/>
+    <numFmt numFmtId="170" formatCode="#,##0&quot; h/yr&quot;"/>
+    <numFmt numFmtId="171" formatCode="#,##0.0&quot; €/MWh&quot;"/>
+    <numFmt numFmtId="172" formatCode="0.0&quot; €/MWh&quot;"/>
+    <numFmt numFmtId="173" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -370,60 +384,28 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="13"/>
       <name val="Cambria"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="9"/>
       <name val="Cambria"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <name val="Cambria"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="12"/>
       <name val="Cambria"/>
-      <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -459,7 +441,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -467,137 +449,39 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -656,15 +540,33 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -701,6 +603,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -719,9 +622,6 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4A7EBB"/>
-            </a:solidFill>
             <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="4A7EBB"/>
@@ -739,6 +639,13 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
@@ -752,6 +659,7 @@
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="r"/>
@@ -760,6 +668,7 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator>; </c:separator>
             <c:showLeaderLines val="0"/>
             <c:extLst>
@@ -769,27 +678,28 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Sensitivity!$A$5:$A$9</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>-20%</c:v>
+                  <c:v>-0.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-10%</c:v>
+                  <c:v>-0.1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0%</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10%</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>0.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -798,24 +708,29 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>294.205381211103</c:v>
+                  <c:v>294.2053812111032</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>228.030966631161</c:v>
+                  <c:v>228.03096663116054</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>186.521696718949</c:v>
+                  <c:v>186.52169671894947</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>158.525671343925</c:v>
+                  <c:v>158.5256713439253</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>138.625693697318</c:v>
+                  <c:v>138.62569369731827</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C008-4A0A-9934-5B672499C5CA}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -832,9 +747,6 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="BE4B48"/>
-            </a:solidFill>
             <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="BE4B48"/>
@@ -852,6 +764,13 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
@@ -865,6 +784,7 @@
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="r"/>
@@ -873,6 +793,7 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator>; </c:separator>
             <c:showLeaderLines val="0"/>
             <c:extLst>
@@ -882,27 +803,28 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Sensitivity!$A$5:$A$9</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>-20%</c:v>
+                  <c:v>-0.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-10%</c:v>
+                  <c:v>-0.1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0%</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10%</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>0.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -911,24 +833,29 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>178.907854076065</c:v>
+                  <c:v>178.90785407606546</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>182.259925240325</c:v>
+                  <c:v>182.25992524032495</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>186.521696718949</c:v>
+                  <c:v>186.52169671894947</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>191.832547542768</c:v>
+                  <c:v>191.83254754276783</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>198.374651581898</c:v>
+                  <c:v>198.37465158189801</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C008-4A0A-9934-5B672499C5CA}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -945,9 +872,6 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="98B855"/>
-            </a:solidFill>
             <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="98B855"/>
@@ -965,6 +889,13 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
@@ -978,6 +909,7 @@
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="r"/>
@@ -986,6 +918,7 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator>; </c:separator>
             <c:showLeaderLines val="0"/>
             <c:extLst>
@@ -995,27 +928,28 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Sensitivity!$A$5:$A$9</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>-20%</c:v>
+                  <c:v>-0.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-10%</c:v>
+                  <c:v>-0.1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0%</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10%</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>0.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1024,24 +958,29 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>221.601571266304</c:v>
+                  <c:v>221.60157126630432</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>202.113645175113</c:v>
+                  <c:v>202.11364517511268</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>186.521696718949</c:v>
+                  <c:v>186.52169671894947</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>173.767570860652</c:v>
+                  <c:v>173.76757086065197</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>163.137792992729</c:v>
+                  <c:v>163.13779299272923</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C008-4A0A-9934-5B672499C5CA}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -1058,9 +997,6 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="7D5FA0"/>
-            </a:solidFill>
             <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="7D5FA0"/>
@@ -1078,6 +1014,13 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
@@ -1091,6 +1034,7 @@
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="r"/>
@@ -1099,6 +1043,7 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator>; </c:separator>
             <c:showLeaderLines val="0"/>
             <c:extLst>
@@ -1108,27 +1053,28 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Sensitivity!$A$5:$A$9</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>-20%</c:v>
+                  <c:v>-0.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-10%</c:v>
+                  <c:v>-0.1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0%</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10%</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>0.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1137,24 +1083,29 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>170.055983549665</c:v>
+                  <c:v>170.05598354966514</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>178.289643925912</c:v>
+                  <c:v>178.28964392591223</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>186.521696718949</c:v>
+                  <c:v>186.52169671894947</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>194.756964678406</c:v>
+                  <c:v>194.75696467840635</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>202.990625054653</c:v>
+                  <c:v>202.99062505465338</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-C008-4A0A-9934-5B672499C5CA}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
@@ -1171,9 +1122,6 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="46AAC4"/>
-            </a:solidFill>
             <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="46AAC4"/>
@@ -1191,6 +1139,13 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
@@ -1204,6 +1159,7 @@
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="r"/>
@@ -1212,6 +1168,7 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator>; </c:separator>
             <c:showLeaderLines val="0"/>
             <c:extLst>
@@ -1221,27 +1178,28 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Sensitivity!$A$5:$A$9</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>-20%</c:v>
+                  <c:v>-0.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-10%</c:v>
+                  <c:v>-0.1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0%</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10%</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>0.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1250,25 +1208,38 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>170.055983549665</c:v>
+                  <c:v>170.05598354966514</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>178.289643925912</c:v>
+                  <c:v>178.28964392591223</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>186.521696718949</c:v>
+                  <c:v>186.52169671894947</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>194.756964678406</c:v>
+                  <c:v>194.75696467840635</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>202.990625054653</c:v>
+                  <c:v>202.99062505465338</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-C008-4A0A-9934-5B672499C5CA}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -1277,6 +1248,7 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
+        <c:smooth val="0"/>
         <c:axId val="47898974"/>
         <c:axId val="46132162"/>
       </c:lineChart>
@@ -1312,6 +1284,7 @@
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="46132162"/>
@@ -1353,6 +1326,7 @@
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="47898974"/>
@@ -1390,11 +1364,13 @@
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1407,227 +1383,16 @@
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataLabel>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <cs:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointMarkerLayout>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1641,14 +1406,20 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>149040</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="2200320"/>
-        <a:ext cx="7918920" cy="3768480"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1662,7 +1433,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1704,12 +1475,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1738,7 +1509,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1759,7 +1530,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1810,7 +1581,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1828,408 +1599,407 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="55"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="5">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="5">
         <v>5</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="1" t="n">
-        <f aca="false">B5+B6</f>
+      <c r="B7">
+        <f>B5+B6</f>
         <v>10</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>4</v>
       </c>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="5">
         <v>2</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="5">
         <v>1120</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>4223.9</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="B10" s="5">
+        <v>4223.8999999999996</v>
+      </c>
+      <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="6" t="n">
-        <v>124.5327</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="B11" s="6">
+        <v>124.53270000000001</v>
+      </c>
+      <c r="C11" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="5">
         <v>20000</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>21</v>
       </c>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="5">
         <v>700000</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>23</v>
       </c>
       <c r="D14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="5">
         <v>400000</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="3"/>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="5">
         <v>2200</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>27</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="5">
         <v>500000</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>30</v>
       </c>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="5">
         <v>2000000</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>32</v>
       </c>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="5">
         <v>500000</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>30</v>
       </c>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="5">
         <v>750000</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>30</v>
       </c>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="5">
         <v>400000</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>36</v>
       </c>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="5">
         <v>3000000</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>38</v>
       </c>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="5">
         <v>2000000</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>30</v>
       </c>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="5">
         <v>10</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>41</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="5">
         <v>0.15</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>44</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+    <row r="27" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="5">
         <v>0.1</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>44</v>
       </c>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>48</v>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="5">
         <v>20</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
         <v>49</v>
       </c>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>50</v>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="5">
         <v>0.95</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s">
         <v>44</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="1" t="n">
-        <f aca="false">B30*8760</f>
+      <c r="B31">
+        <f>B30*8760</f>
         <v>8322</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s">
         <v>53</v>
       </c>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>54</v>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="5">
         <v>13</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s">
         <v>55</v>
       </c>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+    <row r="33" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>56</v>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="5">
         <v>0</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s">
         <v>57</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="1" t="n">
-        <f aca="false">B28*(1+B28)^B29/((1+B28)^B29-1)</f>
-        <v>0.117459624772546</v>
-      </c>
-      <c r="C34" s="1" t="s">
+      <c r="B34">
+        <f>B28*(1+B28)^B29/((1+B28)^B29-1)</f>
+        <v>0.11745962477254576</v>
+      </c>
+      <c r="C34" t="s">
         <v>44</v>
       </c>
       <c r="D34" s="3" t="s">
@@ -2242,745 +2012,716 @@
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A27:D27"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="3" width="14" customWidth="1"/>
+    <col min="4" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="1" t="n">
-        <f aca="false">Assumptions!B10/(1-Assumptions!B25)/1000</f>
-        <v>4.96929411764706</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="B4">
+        <f>Assumptions!B10/(1-Assumptions!B25)/1000</f>
+        <v>4.9692941176470589</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="1" t="n">
-        <f aca="false">Assumptions!B24</f>
+      <c r="C7">
+        <f>Assumptions!B24</f>
         <v>10</v>
       </c>
-      <c r="D7" s="9" t="n">
-        <f aca="false">Assumptions!B13</f>
+      <c r="D7" s="8">
+        <f>Assumptions!B13</f>
         <v>20000</v>
       </c>
-      <c r="E7" s="9" t="n">
-        <f aca="false">C7*D7</f>
+      <c r="E7" s="8">
+        <f t="shared" ref="E7:E17" si="0">C7*D7</f>
         <v>200000</v>
       </c>
-      <c r="F7" s="10" t="n">
-        <f aca="false">E7/$E$18</f>
-        <v>0.0038514430450868</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="F7" s="9">
+        <f t="shared" ref="F7:F17" si="1">E7/$E$18</f>
+        <v>3.8514430450868045E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="1" t="n">
-        <f aca="false">Assumptions!B8</f>
+      <c r="C8">
+        <f>Assumptions!B8</f>
         <v>2</v>
       </c>
-      <c r="D8" s="9" t="n">
-        <f aca="false">Assumptions!B14</f>
+      <c r="D8" s="8">
+        <f>Assumptions!B14</f>
         <v>700000</v>
       </c>
-      <c r="E8" s="9" t="n">
-        <f aca="false">C8*D8</f>
+      <c r="E8" s="8">
+        <f t="shared" si="0"/>
         <v>1400000</v>
       </c>
-      <c r="F8" s="10" t="n">
-        <f aca="false">E8/$E$18</f>
-        <v>0.0269601013156076</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="F8" s="9">
+        <f t="shared" si="1"/>
+        <v>2.6960101315607634E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="1" t="n">
-        <f aca="false">Assumptions!B7</f>
+      <c r="C9">
+        <f>Assumptions!B7</f>
         <v>10</v>
       </c>
-      <c r="D9" s="9" t="n">
-        <f aca="false">Assumptions!B15</f>
+      <c r="D9" s="8">
+        <f>Assumptions!B15</f>
         <v>400000</v>
       </c>
-      <c r="E9" s="9" t="n">
-        <f aca="false">C9*D9</f>
+      <c r="E9" s="8">
+        <f t="shared" si="0"/>
         <v>4000000</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <f aca="false">E9/$E$18</f>
-        <v>0.0770288609017361</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="F9" s="9">
+        <f t="shared" si="1"/>
+        <v>7.7028860901736093E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="1" t="n">
-        <f aca="false">Assumptions!B7*Assumptions!B9</f>
+      <c r="C10">
+        <f>Assumptions!B7*Assumptions!B9</f>
         <v>11200</v>
       </c>
-      <c r="D10" s="9" t="n">
-        <f aca="false">Assumptions!B16</f>
+      <c r="D10" s="8">
+        <f>Assumptions!B16</f>
         <v>2200</v>
       </c>
-      <c r="E10" s="9" t="n">
-        <f aca="false">C10*D10</f>
+      <c r="E10" s="8">
+        <f t="shared" si="0"/>
         <v>24640000</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <f aca="false">E10/$E$18</f>
-        <v>0.474497783154694</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="F10" s="9">
+        <f t="shared" si="1"/>
+        <v>0.47449778315469432</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11">
         <v>1</v>
       </c>
-      <c r="D11" s="9" t="n">
-        <f aca="false">Assumptions!B17</f>
+      <c r="D11" s="8">
+        <f>Assumptions!B17</f>
         <v>500000</v>
       </c>
-      <c r="E11" s="9" t="n">
-        <f aca="false">C11*D11</f>
+      <c r="E11" s="8">
+        <f t="shared" si="0"/>
         <v>500000</v>
       </c>
-      <c r="F11" s="10" t="n">
-        <f aca="false">E11/$E$18</f>
-        <v>0.00962860761271701</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="F11" s="9">
+        <f t="shared" si="1"/>
+        <v>9.6286076127170116E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="1" t="n">
-        <f aca="false">B4</f>
-        <v>4.96929411764706</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <f aca="false">Assumptions!B18</f>
+      <c r="C12">
+        <f>B4</f>
+        <v>4.9692941176470589</v>
+      </c>
+      <c r="D12" s="8">
+        <f>Assumptions!B18</f>
         <v>2000000</v>
       </c>
-      <c r="E12" s="9" t="n">
-        <f aca="false">C12*D12</f>
-        <v>9938588.23529412</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <f aca="false">E12/$E$18</f>
-        <v>0.191389532684025</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="E12" s="8">
+        <f t="shared" si="0"/>
+        <v>9938588.2352941185</v>
+      </c>
+      <c r="F12" s="9">
+        <f t="shared" si="1"/>
+        <v>0.19138953268402537</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13">
         <v>1</v>
       </c>
-      <c r="D13" s="9" t="n">
-        <f aca="false">Assumptions!B19</f>
+      <c r="D13" s="8">
+        <f>Assumptions!B19</f>
         <v>500000</v>
       </c>
-      <c r="E13" s="9" t="n">
-        <f aca="false">C13*D13</f>
+      <c r="E13" s="8">
+        <f t="shared" si="0"/>
         <v>500000</v>
       </c>
-      <c r="F13" s="10" t="n">
-        <f aca="false">E13/$E$18</f>
-        <v>0.00962860761271701</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="F13" s="9">
+        <f t="shared" si="1"/>
+        <v>9.6286076127170116E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14">
         <v>1</v>
       </c>
-      <c r="D14" s="9" t="n">
-        <f aca="false">Assumptions!B20</f>
+      <c r="D14" s="8">
+        <f>Assumptions!B20</f>
         <v>750000</v>
       </c>
-      <c r="E14" s="9" t="n">
-        <f aca="false">C14*D14</f>
+      <c r="E14" s="8">
+        <f t="shared" si="0"/>
         <v>750000</v>
       </c>
-      <c r="F14" s="10" t="n">
-        <f aca="false">E14/$E$18</f>
-        <v>0.0144429114190755</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+      <c r="F14" s="9">
+        <f t="shared" si="1"/>
+        <v>1.4442911419075518E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>80</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>81</v>
       </c>
-      <c r="C15" s="1" t="n">
-        <f aca="false">Assumptions!B5</f>
+      <c r="C15">
+        <f>Assumptions!B5</f>
         <v>5</v>
       </c>
-      <c r="D15" s="9" t="n">
-        <f aca="false">Assumptions!B21</f>
+      <c r="D15" s="8">
+        <f>Assumptions!B21</f>
         <v>400000</v>
       </c>
-      <c r="E15" s="9" t="n">
-        <f aca="false">C15*D15</f>
+      <c r="E15" s="8">
+        <f t="shared" si="0"/>
         <v>2000000</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <f aca="false">E15/$E$18</f>
-        <v>0.0385144304508681</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="F15" s="9">
+        <f t="shared" si="1"/>
+        <v>3.8514430450868047E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>82</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="1" t="n">
-        <f aca="false">Assumptions!B8</f>
+      <c r="C16">
+        <f>Assumptions!B8</f>
         <v>2</v>
       </c>
-      <c r="D16" s="9" t="n">
-        <f aca="false">Assumptions!B22</f>
+      <c r="D16" s="8">
+        <f>Assumptions!B22</f>
         <v>3000000</v>
       </c>
-      <c r="E16" s="9" t="n">
-        <f aca="false">C16*D16</f>
+      <c r="E16" s="8">
+        <f t="shared" si="0"/>
         <v>6000000</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <f aca="false">E16/$E$18</f>
-        <v>0.115543291352604</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="F16" s="9">
+        <f t="shared" si="1"/>
+        <v>0.11554329135260415</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>84</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n">
-        <f aca="false">Assumptions!B23</f>
+      <c r="D17" s="8">
+        <f>Assumptions!B23</f>
         <v>2000000</v>
       </c>
-      <c r="E17" s="9" t="n">
-        <f aca="false">C17*D17</f>
+      <c r="E17" s="8">
+        <f t="shared" si="0"/>
         <v>2000000</v>
       </c>
-      <c r="F17" s="10" t="n">
-        <f aca="false">E17/$E$18</f>
-        <v>0.0385144304508681</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="s">
+      <c r="F17" s="9">
+        <f t="shared" si="1"/>
+        <v>3.8514430450868047E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="14" t="n">
-        <f aca="false">SUM(E7:E17)</f>
-        <v>51928588.2352941</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="13">
+        <f>SUM(E7:E17)</f>
+        <v>51928588.235294119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B20" s="15" t="n">
-        <f aca="false">E18/Assumptions!B10</f>
-        <v>12293.9909172315</v>
+      <c r="B20" s="14">
+        <f>E18/Assumptions!B10</f>
+        <v>12293.990917231498</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="9" t="n">
-        <f aca="false">CAPEX_Group3!E18</f>
-        <v>51928588.2352941</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="B4" s="8">
+        <f>CAPEX_Group3!E18</f>
+        <v>51928588.235294119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="16" t="n">
-        <f aca="false">Assumptions!B10</f>
-        <v>4223.9</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="B5" s="15">
+        <f>Assumptions!B10</f>
+        <v>4223.8999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="15" t="n">
-        <f aca="false">B4/B5</f>
-        <v>12293.9909172315</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="B6" s="14">
+        <f>B4/B5</f>
+        <v>12293.990917231498</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="6" t="n">
-        <f aca="false">Assumptions!B34</f>
-        <v>0.117459624772546</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="B7" s="6">
+        <f>Assumptions!B34</f>
+        <v>0.11745962477254576</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="17" t="n">
-        <f aca="false">Assumptions!B33</f>
+      <c r="B8" s="16">
+        <f>Assumptions!B33</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="18" t="n">
-        <f aca="false">Assumptions!B31</f>
+      <c r="B9" s="17">
+        <f>Assumptions!B31</f>
         <v>8322</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="19" t="n">
-        <f aca="false">Assumptions!B32</f>
+      <c r="B10" s="18">
+        <f>Assumptions!B32</f>
         <v>13</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
+    <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="B12" s="21" t="n">
-        <f aca="false">(B6*B7+B8)/B9*1000+B10</f>
-        <v>186.521696718949</v>
+      <c r="B12" s="20">
+        <f>(B6*B7+B8)/B9*1000+B10</f>
+        <v>186.52169671894947</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="4" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="n">
+    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="21">
         <v>-0.2</v>
       </c>
-      <c r="B5" s="1" t="n">
-        <f aca="false">Assumptions!$B$11*(1+A5)</f>
-        <v>99.62616</v>
-      </c>
-      <c r="C5" s="23" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((B5)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B5)-(50))/LN((273.15+(B5))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((B5)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B5)-(50))/LN((273.15+(B5))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>294.205381211103</v>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="B5">
+        <f>Assumptions!$B$11*(1+A5)</f>
+        <v>99.626160000000013</v>
+      </c>
+      <c r="C5" s="22">
+        <f>(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((B5)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B5)-(50))/LN((273.15+(B5))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((B5)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B5)-(50))/LN((273.15+(B5))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>294.2053812111032</v>
+      </c>
+      <c r="D5">
         <v>40</v>
       </c>
-      <c r="E5" s="23" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(40)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(40))/LN((273.15+(Assumptions!$B$11))/(273.15+(40)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(40)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(40))/LN((273.15+(Assumptions!$B$11))/(273.15+(40)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>178.907854076065</v>
-      </c>
-      <c r="F5" s="1" t="n">
+      <c r="E5" s="22">
+        <f>(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(40)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(40))/LN((273.15+(Assumptions!$B$11))/(273.15+(40)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(40)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(40))/LN((273.15+(Assumptions!$B$11))/(273.15+(40)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>178.90785407606546</v>
+      </c>
+      <c r="F5">
         <v>120</v>
       </c>
-      <c r="G5" s="23" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((120)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((120)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>221.601571266304</v>
-      </c>
-      <c r="H5" s="1" t="n">
+      <c r="G5" s="22">
+        <f>(((17350000+((2200)*(1120)*10)+(2000000*(((((120)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((120)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>221.60157126630432</v>
+      </c>
+      <c r="H5">
         <v>896</v>
       </c>
-      <c r="I5" s="23" t="n">
-        <f aca="false">(((17350000+((2200)*(896)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>170.055983549665</v>
-      </c>
-      <c r="J5" s="1" t="n">
+      <c r="I5" s="22">
+        <f>(((17350000+((2200)*(896)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>170.05598354966514</v>
+      </c>
+      <c r="J5">
         <v>1760</v>
       </c>
-      <c r="K5" s="23" t="n">
-        <f aca="false">(((17350000+((1760)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>170.055983549665</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="n">
+      <c r="K5" s="22">
+        <f>(((17350000+((1760)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>170.05598354966514</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="21">
         <v>-0.1</v>
       </c>
-      <c r="B6" s="1" t="n">
-        <f aca="false">Assumptions!$B$11*(1+A6)</f>
+      <c r="B6">
+        <f>Assumptions!$B$11*(1+A6)</f>
         <v>112.07943</v>
       </c>
-      <c r="C6" s="23" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((B6)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B6)-(50))/LN((273.15+(B6))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((B6)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B6)-(50))/LN((273.15+(B6))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>228.030966631161</v>
-      </c>
-      <c r="D6" s="1" t="n">
+      <c r="C6" s="22">
+        <f>(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((B6)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B6)-(50))/LN((273.15+(B6))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((B6)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B6)-(50))/LN((273.15+(B6))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>228.03096663116054</v>
+      </c>
+      <c r="D6">
         <v>45</v>
       </c>
-      <c r="E6" s="23" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(45)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(45))/LN((273.15+(Assumptions!$B$11))/(273.15+(45)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(45)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(45))/LN((273.15+(Assumptions!$B$11))/(273.15+(45)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>182.259925240325</v>
-      </c>
-      <c r="F6" s="1" t="n">
+      <c r="E6" s="22">
+        <f>(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(45)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(45))/LN((273.15+(Assumptions!$B$11))/(273.15+(45)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(45)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(45))/LN((273.15+(Assumptions!$B$11))/(273.15+(45)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>182.25992524032495</v>
+      </c>
+      <c r="F6">
         <v>135</v>
       </c>
-      <c r="G6" s="23" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((135)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((135)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>202.113645175113</v>
-      </c>
-      <c r="H6" s="1" t="n">
+      <c r="G6" s="22">
+        <f>(((17350000+((2200)*(1120)*10)+(2000000*(((((135)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((135)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>202.11364517511268</v>
+      </c>
+      <c r="H6">
         <v>1008</v>
       </c>
-      <c r="I6" s="23" t="n">
-        <f aca="false">(((17350000+((2200)*(1008)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>178.289643925912</v>
-      </c>
-      <c r="J6" s="1" t="n">
+      <c r="I6" s="22">
+        <f>(((17350000+((2200)*(1008)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>178.28964392591223</v>
+      </c>
+      <c r="J6">
         <v>1980</v>
       </c>
-      <c r="K6" s="23" t="n">
-        <f aca="false">(((17350000+((1980)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>178.289643925912</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="n">
+      <c r="K6" s="22">
+        <f>(((17350000+((1980)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>178.28964392591223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="21">
         <v>0</v>
       </c>
-      <c r="B7" s="6" t="n">
-        <f aca="false">Assumptions!$B$11</f>
-        <v>124.5327</v>
-      </c>
-      <c r="C7" s="23" t="n">
-        <f aca="false">LCOE_Group3!$B$12</f>
-        <v>186.521696718949</v>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="B7" s="6">
+        <f>Assumptions!$B$11</f>
+        <v>124.53270000000001</v>
+      </c>
+      <c r="C7" s="22">
+        <f>LCOE_Group3!$B$12</f>
+        <v>186.52169671894947</v>
+      </c>
+      <c r="D7">
         <v>50</v>
       </c>
-      <c r="E7" s="23" t="n">
-        <f aca="false">LCOE_Group3!$B$12</f>
-        <v>186.521696718949</v>
-      </c>
-      <c r="F7" s="1" t="n">
+      <c r="E7" s="22">
+        <f>LCOE_Group3!$B$12</f>
+        <v>186.52169671894947</v>
+      </c>
+      <c r="F7">
         <v>150</v>
       </c>
-      <c r="G7" s="23" t="n">
-        <f aca="false">LCOE_Group3!$B$12</f>
-        <v>186.521696718949</v>
-      </c>
-      <c r="H7" s="1" t="n">
+      <c r="G7" s="22">
+        <f>LCOE_Group3!$B$12</f>
+        <v>186.52169671894947</v>
+      </c>
+      <c r="H7">
         <v>1120</v>
       </c>
-      <c r="I7" s="23" t="n">
-        <f aca="false">LCOE_Group3!$B$12</f>
-        <v>186.521696718949</v>
-      </c>
-      <c r="J7" s="1" t="n">
+      <c r="I7" s="22">
+        <f>LCOE_Group3!$B$12</f>
+        <v>186.52169671894947</v>
+      </c>
+      <c r="J7">
         <v>2200</v>
       </c>
-      <c r="K7" s="23" t="n">
-        <f aca="false">LCOE_Group3!$B$12</f>
-        <v>186.521696718949</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="n">
+      <c r="K7" s="22">
+        <f>LCOE_Group3!$B$12</f>
+        <v>186.52169671894947</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="21">
         <v>0.1</v>
       </c>
-      <c r="B8" s="1" t="n">
-        <f aca="false">Assumptions!$B$11*(1+A8)</f>
-        <v>136.98597</v>
-      </c>
-      <c r="C8" s="23" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((B8)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B8)-(50))/LN((273.15+(B8))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((B8)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B8)-(50))/LN((273.15+(B8))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>158.525671343925</v>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B8">
+        <f>Assumptions!$B$11*(1+A8)</f>
+        <v>136.98597000000001</v>
+      </c>
+      <c r="C8" s="22">
+        <f>(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((B8)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B8)-(50))/LN((273.15+(B8))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((B8)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B8)-(50))/LN((273.15+(B8))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>158.5256713439253</v>
+      </c>
+      <c r="D8">
         <v>55</v>
       </c>
-      <c r="E8" s="23" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(55)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(55))/LN((273.15+(Assumptions!$B$11))/(273.15+(55)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(55)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(55))/LN((273.15+(Assumptions!$B$11))/(273.15+(55)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>191.832547542768</v>
-      </c>
-      <c r="F8" s="1" t="n">
+      <c r="E8" s="22">
+        <f>(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(55)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(55))/LN((273.15+(Assumptions!$B$11))/(273.15+(55)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(55)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(55))/LN((273.15+(Assumptions!$B$11))/(273.15+(55)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>191.83254754276783</v>
+      </c>
+      <c r="F8">
         <v>165</v>
       </c>
-      <c r="G8" s="23" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((165)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((165)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>173.767570860652</v>
-      </c>
-      <c r="H8" s="1" t="n">
+      <c r="G8" s="22">
+        <f>(((17350000+((2200)*(1120)*10)+(2000000*(((((165)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((165)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>173.76757086065197</v>
+      </c>
+      <c r="H8">
         <v>1232</v>
       </c>
-      <c r="I8" s="23" t="n">
-        <f aca="false">(((17350000+((2200)*(1232)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>194.756964678406</v>
-      </c>
-      <c r="J8" s="1" t="n">
+      <c r="I8" s="22">
+        <f>(((17350000+((2200)*(1232)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>194.75696467840635</v>
+      </c>
+      <c r="J8">
         <v>2420</v>
       </c>
-      <c r="K8" s="23" t="n">
-        <f aca="false">(((17350000+((2420)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>194.756964678406</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="n">
+      <c r="K8" s="22">
+        <f>(((17350000+((2420)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>194.75696467840635</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="21">
         <v>0.2</v>
       </c>
-      <c r="B9" s="1" t="n">
-        <f aca="false">Assumptions!$B$11*(1+A9)</f>
-        <v>149.43924</v>
-      </c>
-      <c r="C9" s="23" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((B9)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B9)-(50))/LN((273.15+(B9))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((B9)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B9)-(50))/LN((273.15+(B9))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>138.625693697318</v>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B9">
+        <f>Assumptions!$B$11*(1+A9)</f>
+        <v>149.43924000000001</v>
+      </c>
+      <c r="C9" s="22">
+        <f>(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((B9)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B9)-(50))/LN((273.15+(B9))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((B9)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((B9)-(50))/LN((273.15+(B9))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>138.62569369731827</v>
+      </c>
+      <c r="D9">
         <v>60</v>
       </c>
-      <c r="E9" s="23" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(60)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(60))/LN((273.15+(Assumptions!$B$11))/(273.15+(60)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(60)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(60))/LN((273.15+(Assumptions!$B$11))/(273.15+(60)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>198.374651581898</v>
-      </c>
-      <c r="F9" s="1" t="n">
+      <c r="E9" s="22">
+        <f>(((17350000+((2200)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(60)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(60))/LN((273.15+(Assumptions!$B$11))/(273.15+(60)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(60)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(60))/LN((273.15+(Assumptions!$B$11))/(273.15+(60)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>198.37465158189801</v>
+      </c>
+      <c r="F9">
         <v>180</v>
       </c>
-      <c r="G9" s="23" t="n">
-        <f aca="false">(((17350000+((2200)*(1120)*10)+(2000000*(((((180)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((180)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>163.137792992729</v>
-      </c>
-      <c r="H9" s="1" t="n">
+      <c r="G9" s="22">
+        <f>(((17350000+((2200)*(1120)*10)+(2000000*(((((180)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((180)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>163.13779299272923</v>
+      </c>
+      <c r="H9">
         <v>1344</v>
       </c>
-      <c r="I9" s="23" t="n">
-        <f aca="false">(((17350000+((2200)*(1344)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>202.990625054653</v>
-      </c>
-      <c r="J9" s="1" t="n">
+      <c r="I9" s="22">
+        <f>(((17350000+((2200)*(1344)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>202.99062505465338</v>
+      </c>
+      <c r="J9">
         <v>2640</v>
       </c>
-      <c r="K9" s="23" t="n">
-        <f aca="false">(((17350000+((2640)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
-        <v>202.990625054653</v>
+      <c r="K9" s="22">
+        <f>(((17350000+((2640)*(1120)*10)+(2000000*(((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15)))))/0.85/1000)))/((((150)*0.917)*4.31*((Assumptions!$B$11)-(50)))*(0.52*(1-(273.15+19.9590607511086)/(273.15+(((Assumptions!$B$11)-(50))/LN((273.15+(Assumptions!$B$11))/(273.15+(50)))-273.15))))))*0.117459624772546)/8322*1000+13</f>
+        <v>202.99062505465338</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>